--- a/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -880,30 +881,35 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -928,22 +934,27 @@
           <t>Lincolnton</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -968,22 +979,27 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1008,22 +1024,27 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1048,22 +1069,27 @@
           <t>Kumamoto Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1088,22 +1114,27 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1128,22 +1159,27 @@
           <t>Collinsville Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1168,22 +1204,27 @@
           <t>Durham Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1208,22 +1249,27 @@
           <t>Granbury Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1248,22 +1294,27 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1288,22 +1339,27 @@
           <t>Santa Rosa</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1328,22 +1384,27 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1368,22 +1429,27 @@
           <t>Pekín</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0</v>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1408,22 +1474,27 @@
           <t>Longview Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1448,22 +1519,27 @@
           <t>North Sea Coast Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1488,22 +1564,27 @@
           <t>Santiago de Chile Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="13" t="n">
+      <c r="H20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="13" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1528,22 +1609,27 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>0.07692307692307693</v>
+      <c r="H21" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="13" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1568,22 +1654,27 @@
           <t>Monterrey</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="G22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="13" t="n">
-        <v>0.08333333333333333</v>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="13" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1608,22 +1699,27 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1648,22 +1744,27 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="13" t="n">
         <v>0.273972602739726</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.00684931506849315</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1688,22 +1789,27 @@
           <t>Aruba</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.3448275862068966</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1728,22 +1834,27 @@
           <t>Varadero</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="13" t="n">
         <v>0.3483146067415731</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>0.01123595505617977</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1768,22 +1879,27 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="13" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1808,22 +1924,27 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="J28" s="13" t="n">
         <v>0.0625</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1848,22 +1969,27 @@
           <t>Santa Marta Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1888,22 +2014,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>1026</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.5701754385964912</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>0.01461988304093567</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1928,22 +2059,27 @@
           <t>Los Cabos Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="J31" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1968,22 +2104,27 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2008,22 +2149,27 @@
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.625</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2048,22 +2194,27 @@
           <t>Orange County Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="13" t="n">
+      <c r="H34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2088,22 +2239,27 @@
           <t>Lethbridge Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2128,22 +2284,27 @@
           <t>Chiba Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2168,22 +2329,27 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13" t="n">
         <v>0.6911764705882353</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>0.007352941176470588</v>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2208,22 +2374,27 @@
           <t>Panama City Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>0.0375</v>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2248,22 +2419,27 @@
           <t>Bogotá Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2288,22 +2464,27 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="13" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2328,22 +2509,27 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2368,22 +2554,27 @@
           <t>Luray Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="13" t="n">
+      <c r="H42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="I42" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2408,22 +2599,27 @@
           <t>Manzanillo</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="J43" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2448,22 +2644,27 @@
           <t>Tamaulipas</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="13" t="n">
+      <c r="H44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="13" t="n">
         <v>0.759493670886076</v>
       </c>
-      <c r="I44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2488,22 +2689,27 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.7671232876712328</v>
       </c>
-      <c r="I45" s="13" t="n">
+      <c r="J45" s="13" t="n">
         <v>0.0136986301369863</v>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2528,22 +2734,27 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="13" t="n">
+      <c r="H46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="13" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="I46" s="13" t="n">
+      <c r="J46" s="13" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2568,22 +2779,27 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="13" t="n">
+      <c r="H47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="13" t="n">
         <v>0.775</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2608,22 +2824,27 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="13" t="n">
+      <c r="H48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.7843137254901961</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>0.009803921568627451</v>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2648,22 +2869,27 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.7951807228915663</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>0.02409638554216868</v>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2688,22 +2914,27 @@
           <t>Oaxaca</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="13" t="n">
+      <c r="H50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="13" t="n">
         <v>0.8</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2728,22 +2959,27 @@
           <t>Puerto Escondido Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.8048780487804879</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.01742160278745645</v>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2768,22 +3004,27 @@
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="13" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2808,22 +3049,27 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="13" t="n">
+      <c r="H53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2848,22 +3094,27 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="13" t="n">
+      <c r="H54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2888,22 +3139,27 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G55" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="13" t="n">
+      <c r="H55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="13" t="n">
         <v>0.8367346938775511</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2920,18 +3176,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2951,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2978,25 +3235,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -3021,19 +3283,24 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>2143</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="n">
         <v>0.9986000933271115</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.0004666355576294914</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3058,19 +3325,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="F7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
         <v>0.9717125382262997</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.0007645259938837921</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3095,19 +3367,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>1138</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="n">
         <v>0.9859402460456942</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.0008787346221441124</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3132,19 +3409,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>1134</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9929453262786596</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.002645502645502645</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3169,19 +3451,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>1026</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.5701754385964912</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.01461988304093567</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3206,19 +3493,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>1006</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9910536779324056</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.001988071570576541</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3243,19 +3535,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>860</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9895348837209302</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.003488372093023256</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3280,19 +3577,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>853</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.8780773739742087</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.003516998827667058</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3317,19 +3619,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="13" t="n">
         <v>0.002366863905325444</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3354,19 +3661,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9763313609467456</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.003550295857988166</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3391,19 +3703,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>810</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.9518518518518518</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.004938271604938272</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3428,19 +3745,24 @@
           <t>Acapulco</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>767</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9556714471968709</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.01303780964797914</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3465,19 +3787,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>0.9735294117647059</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.001470588235294118</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3502,19 +3829,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>664</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="13" t="n">
         <v>0.004518072289156626</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3539,19 +3871,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>0.9908814589665653</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.001519756838905775</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3576,19 +3913,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9983870967741936</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.004838709677419355</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3613,19 +3955,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9875518672199171</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3650,19 +3997,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>467</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>0.9036402569593148</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.002141327623126338</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3687,19 +4039,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.002197802197802198</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3724,19 +4081,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9910714285714286</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.006696428571428571</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3761,19 +4123,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9907621247113164</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.006928406466512702</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3798,19 +4165,24 @@
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9976905311778291</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.0115473441108545</v>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3835,19 +4207,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>429</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>0.9813519813519813</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002331002331002331</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3872,19 +4249,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3909,19 +4291,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>419</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.002386634844868735</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3946,19 +4333,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>0.9878048780487805</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3983,19 +4375,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>376</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>0.9893617021276596</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.002659574468085106</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4020,19 +4417,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>0.8435754189944135</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.002793296089385475</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4057,19 +4459,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>0.9943977591036415</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.002801120448179272</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4094,19 +4501,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>334</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9910179640718563</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.005988023952095809</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4131,19 +4543,24 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>331</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.945619335347432</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.006042296072507553</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4168,19 +4585,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.8792569659442725</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.009287925696594427</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4205,19 +4627,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="13" t="n">
         <v>0.003412969283276451</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4242,19 +4669,24 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13" t="n">
         <v>0.003484320557491289</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4279,19 +4711,24 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13" t="n">
         <v>0.8960573476702509</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.003584229390681004</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4316,19 +4753,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
         <v>0.9922178988326849</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.003891050583657588</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4353,19 +4795,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="13" t="n">
         <v>0.008032128514056224</v>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4390,19 +4837,24 @@
           <t>Mazatlán</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0.008130081300813009</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4427,19 +4879,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9915966386554622</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.01260504201680672</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4464,19 +4921,24 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="13" t="n">
         <v>0.9220779220779221</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.004329004329004329</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4501,19 +4963,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="13" t="n">
         <v>0.9956331877729258</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4538,19 +5005,24 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="n">
         <v>0.982532751091703</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4575,19 +5047,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="13" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.004484304932735426</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4612,19 +5089,24 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="F49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13" t="n">
         <v>0.9908675799086758</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.0045662100456621</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4649,19 +5131,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4686,19 +5173,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="13" t="n">
         <v>0.01415094339622642</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4723,19 +5215,24 @@
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="13" t="n">
         <v>0.9716981132075472</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.004716981132075472</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4760,19 +5257,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4797,19 +5299,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="13" t="n">
+      <c r="G54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13" t="n">
         <v>0.994413407821229</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.00558659217877095</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4834,19 +5341,24 @@
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9943502824858758</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.01129943502824859</v>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4863,18 +5375,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4894,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4921,25 +5434,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -4964,19 +5482,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>3087</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="n">
         <v>0.07223841917719469</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5001,19 +5524,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>2426</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>2363</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="n">
         <v>0.9740313272877164</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5038,19 +5566,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>2163</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>2106</v>
       </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="n">
         <v>0.9736477115117892</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5075,19 +5608,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>1928</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>1910</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>0.9906639004149378</v>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5112,19 +5650,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>1588</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="n">
         <v>0.1309823677581864</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5149,19 +5692,24 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>1301</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1289</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="n">
         <v>0.9907763259031515</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5186,19 +5734,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>1209</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="n">
         <v>0.5260545905707196</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5223,19 +5776,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>1057</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>840</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
         <v>0.7947019867549668</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5260,19 +5818,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>995</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="n">
         <v>0.995</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5297,19 +5860,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>884</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
         <v>0.973568281938326</v>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5334,19 +5902,24 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>791</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>754</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13" t="n">
         <v>0.9532237673830595</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5371,19 +5944,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>782</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>773</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>0.9884910485933504</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5408,19 +5986,24 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>743</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>349</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13" t="n">
         <v>0.4697173620457604</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5445,19 +6028,24 @@
           <t>Aruba</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>736</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>724</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13" t="n">
         <v>0.9836956521739131</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5482,19 +6070,24 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
-        <v>727</v>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F20" s="12" t="n">
         <v>727</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+        <v>727</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5519,19 +6112,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>727</v>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F21" s="12" t="n">
         <v>727</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
+        <v>727</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5556,19 +6154,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>692</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>691</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13" t="n">
         <v>0.9985549132947977</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5593,19 +6196,24 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>690</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>682</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13" t="n">
         <v>0.9884057971014493</v>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5630,19 +6238,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>686</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>665</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13" t="n">
         <v>0.9693877551020408</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5667,19 +6280,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>676</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13" t="n">
         <v>0.9866863905325444</v>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5704,19 +6322,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>662</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>625</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13" t="n">
         <v>0.9441087613293051</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5741,19 +6364,24 @@
           <t>Montreal</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>650</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13" t="n">
         <v>0.9878419452887538</v>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5778,19 +6406,24 @@
           <t>Jacksonville Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>654</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>646</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13" t="n">
         <v>0.9877675840978594</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5815,19 +6448,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
-        <v>619</v>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F29" s="12" t="n">
         <v>619</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+        <v>619</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5852,19 +6490,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>603</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>602</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13" t="n">
+      <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>0.9983416252072969</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5889,19 +6532,24 @@
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
-        <v>572</v>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F31" s="12" t="n">
         <v>572</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+        <v>572</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5926,19 +6574,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>532</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="13" t="n">
         <v>0.9830827067669173</v>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5963,19 +6616,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>521</v>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>521</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+        <v>521</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6000,19 +6658,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>514</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>508</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="13" t="n">
+      <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13" t="n">
         <v>0.9883268482490273</v>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6037,19 +6700,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>485</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13" t="n">
         <v>0.9917525773195877</v>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6074,19 +6742,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>459</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13" t="n">
         <v>0.9935064935064936</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6111,19 +6784,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>443</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>442</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13" t="n">
         <v>0.9977426636568849</v>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6148,19 +6826,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>439</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="13" t="n">
+      <c r="H38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13" t="n">
         <v>0.9840546697038725</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6185,19 +6868,24 @@
           <t>Pittsburgh Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>433</v>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F39" s="12" t="n">
         <v>433</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
+        <v>433</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6222,19 +6910,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>406</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13" t="n">
         <v>0.9398148148148148</v>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6259,19 +6952,24 @@
           <t>Tampa Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>420</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>416</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13" t="n">
         <v>0.9904761904761905</v>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6296,19 +6994,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>419</v>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F42" s="12" t="n">
         <v>419</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+        <v>419</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6333,19 +7036,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>416</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>414</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0.9951923076923077</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6370,19 +7078,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>405</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>398</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="13" t="n">
+      <c r="H44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13" t="n">
         <v>0.9827160493827161</v>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6407,19 +7120,24 @@
           <t>Sheridan Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
-        <v>400</v>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F45" s="12" t="n">
         <v>400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+        <v>400</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6444,19 +7162,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>399</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="13" t="n">
+      <c r="H46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13" t="n">
         <v>0.9147869674185464</v>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6481,19 +7204,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
-        <v>399</v>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F47" s="12" t="n">
         <v>399</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6518,19 +7246,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>385</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="13" t="n">
+      <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.9896103896103896</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6555,19 +7288,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>382</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>374</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="13" t="n">
+      <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13" t="n">
         <v>0.9790575916230366</v>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6592,19 +7330,24 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>380</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="13" t="n">
+      <c r="H50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13" t="n">
         <v>0.9973753280839895</v>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6629,19 +7372,24 @@
           <t>West Palm Beach Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>379</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="13" t="n">
+      <c r="H51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13" t="n">
         <v>0.9973614775725593</v>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6666,19 +7414,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>373</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13" t="n">
         <v>0.9867724867724867</v>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6703,19 +7456,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>374</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>372</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="13" t="n">
+      <c r="H53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>0.9946524064171123</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6740,19 +7498,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>372</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="13" t="n">
+      <c r="H54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13" t="n">
         <v>0.9811827956989247</v>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6777,19 +7540,24 @@
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>370</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>366</v>
       </c>
-      <c r="G55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="13" t="n">
+      <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13" t="n">
         <v>0.9891891891891892</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6837,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +11291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10830,18 +11598,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10861,7 +11630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10888,25 +11657,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -10931,19 +11705,24 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10968,19 +11747,24 @@
           <t>Pekín</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11005,19 +11789,24 @@
           <t>Lincolnton</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11042,19 +11831,24 @@
           <t>Granbury Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11079,19 +11873,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11116,19 +11915,24 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11153,19 +11957,24 @@
           <t>Kumamoto Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11190,19 +11999,24 @@
           <t>Honshū Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11227,19 +12041,24 @@
           <t>Durham Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11264,19 +12083,24 @@
           <t>North Sea Coast Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11301,19 +12125,24 @@
           <t>Santa Rosa</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11338,19 +12167,24 @@
           <t>Longview Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0</v>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11375,19 +12209,24 @@
           <t>Collinsville Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11412,19 +12251,24 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11449,19 +12293,24 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>2143</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>0.9986000933271115</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.0004666355576294914</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11486,19 +12335,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>0.9717125382262997</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.0007645259938837921</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11523,19 +12377,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>1138</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>0.9859402460456942</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.0008787346221441124</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11560,19 +12419,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>0.9735294117647059</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.001470588235294118</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11597,19 +12461,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>0.9908814589665653</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.001519756838905775</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11634,19 +12503,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>1006</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9910536779324056</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.001988071570576541</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11671,19 +12545,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>467</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="13" t="n">
         <v>0.9036402569593148</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.002141327623126338</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11708,19 +12587,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.002197802197802198</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11745,19 +12629,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>429</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>0.9813519813519813</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002331002331002331</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11782,19 +12671,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11819,19 +12713,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>0.002366863905325444</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11856,19 +12755,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>419</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.002386634844868735</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11893,19 +12797,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>0.9878048780487805</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11930,19 +12839,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>1134</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9929453262786596</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.002645502645502645</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11967,19 +12881,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>376</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>0.9893617021276596</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.002659574468085106</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12004,19 +12923,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="13" t="n">
         <v>0.8435754189944135</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.002793296089385475</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12041,19 +12965,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="13" t="n">
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>0.9943977591036415</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.002801120448179272</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12078,19 +13007,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13" t="n">
         <v>0.003412969283276451</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12115,19 +13049,24 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="13" t="n">
         <v>0.003484320557491289</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12152,19 +13091,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>860</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9895348837209302</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.003488372093023256</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12189,19 +13133,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>853</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.8780773739742087</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.003516998827667058</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12226,19 +13175,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9763313609467456</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.003550295857988166</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12263,19 +13217,24 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="13" t="n">
+      <c r="G42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>0.8960573476702509</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.003584229390681004</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12300,19 +13259,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="13" t="n">
         <v>0.9922178988326849</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.003891050583657588</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12337,19 +13301,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9875518672199171</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12374,19 +13343,24 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="13" t="n">
         <v>0.9220779220779221</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.004329004329004329</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12411,19 +13385,24 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="13" t="n">
         <v>0.982532751091703</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12448,19 +13427,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="n">
         <v>0.9956331877729258</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12485,19 +13469,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="13" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.004484304932735426</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12522,19 +13511,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>664</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="13" t="n">
         <v>0.004518072289156626</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12559,19 +13553,24 @@
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="13" t="n">
         <v>0.9908675799086758</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.0045662100456621</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12596,19 +13595,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12633,19 +13637,24 @@
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="13" t="n">
         <v>0.9716981132075472</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.004716981132075472</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12670,19 +13679,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.9983870967741936</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.004838709677419355</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12707,19 +13721,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>810</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9518518518518518</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.004938271604938272</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12744,19 +13763,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F55" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="13" t="n">
+      <c r="G55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="13" t="n">
         <v>0.994413407821229</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.00558659217877095</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7489,18 +7489,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7520,7 +7520,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7918,6 +7918,1406 @@
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4297</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>4139</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.9632301605771468</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.008145217593670002</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>4295</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>4207</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9795110593713621</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.0006984866123399302</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>3959</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>3807</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9616064662793635</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.04041424602172266</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>3612</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.9517786561264822</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.0007905138339920949</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>3341</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>3297</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9868302903322359</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.002095181083507932</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>3281</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>2915</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.8884486437061871</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.0003047851264858275</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>3071</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>2976</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9690654509931619</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.001302507326603712</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>2962</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9743421052631579</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.01151315789473684</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9745762711864406</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.0006779661016949153</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>2788</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9637054960248876</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.001036985827860353</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>2785</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>2731</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9806104129263914</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.000718132854578097</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Acapulco</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>2758</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.9579405366207396</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.03734590282813633</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>2745</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>2347</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.8550091074681239</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.02003642987249545</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>2660</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>2632</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9894736842105263</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.0007518796992481203</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>2618</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>2590</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.9893048128342246</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.001145912910618793</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>2558</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.9868827160493827</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.001157407407407407</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>2577</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2551</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9899107489328677</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.001552192471866511</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Niagara Falls, Canada</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>2520</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.998019801980198</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.0003960396039603961</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>2332</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.9426030719482619</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.0004042037186742118</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>2437</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>2415</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9909725071809602</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>2051</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>1507</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.734763529985373</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.003412969283276451</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>2038</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.9906771344455348</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.01030421982335623</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9872068230277186</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.002132196162046908</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>1830</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9775956284153006</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.000546448087431694</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia (and vicinity), PA, US</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1711</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1677</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.9801285797779077</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1706</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9630715123094959</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.007033997655334115</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Washington, DC Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.9791395045632334</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.001303780964797914</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ixtapa / Zihuatanejo</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>1486</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>1365</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9185733512786003</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.008075370121130552</v>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Area</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.978839590443686</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.0006825938566552901</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Pittsburgh Area</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>1446</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.9897330595482546</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>1444</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.7915512465373962</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.04155124653739612</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Medellin Area</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>1426</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.9523141654978962</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.01332398316970547</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Jacksonville Area</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>1321</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9841029523088569</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.002271006813020439</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>1237</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.973249409913454</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.002360346184107002</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>1252</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.987220447284345</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.004792332268370607</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Minneapolis - St. Paul Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>1214</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9814066289409863</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.003233629749393694</v>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Detroit Area</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9859387923904053</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Santa Marta Area</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1156</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.990484429065744</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.02076124567474048</v>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Mazatlán</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9911426040744021</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.01505757307351639</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>1074</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.9521276595744681</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -7963,7 +9363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8301,7 +9701,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -875,35 +876,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -925,25 +931,30 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Santiago de Chile Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="13" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="J6" s="13" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -965,25 +976,30 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="13" t="n">
         <v>0.273972602739726</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="J7" s="13" t="n">
         <v>0.00684931506849315</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1005,25 +1021,30 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.3448275862068966</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="J8" s="13" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1045,25 +1066,30 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Varadero</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>0.3483146067415731</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="J9" s="13" t="n">
         <v>0.01123595505617977</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1085,25 +1111,30 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="J10" s="13" t="n">
         <v>0.0625</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1125,25 +1156,30 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1026</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.5701754385964912</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.01461988304093567</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1165,25 +1201,30 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>264</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="J12" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1205,25 +1246,30 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="13" t="n">
         <v>0.6911764705882353</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>0.007352941176470588</v>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1245,25 +1291,30 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Panama City Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>0.0375</v>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1285,25 +1336,30 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Tamaulipas</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13" t="n">
         <v>0.759493670886076</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="J15" s="13" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1325,25 +1381,30 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.7671232876712328</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="J16" s="13" t="n">
         <v>0.0136986301369863</v>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1365,25 +1426,30 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>0.775</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1405,25 +1471,30 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="13" t="n">
         <v>0.7843137254901961</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="J18" s="13" t="n">
         <v>0.009803921568627451</v>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1445,25 +1516,30 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.7951807228915663</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="J19" s="13" t="n">
         <v>0.02409638554216868</v>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1485,25 +1561,30 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Puerto Escondido Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.8048780487804879</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.01742160278745645</v>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1525,25 +1606,30 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>San Antonio</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="13" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1565,25 +1651,30 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1605,25 +1696,30 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
         <v>0.8367346938775511</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1645,25 +1741,30 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.8375</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.01875</v>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1685,25 +1786,30 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.8387096774193549</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1725,25 +1831,30 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="13" t="n">
         <v>0.8435754189944135</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>0.002793296089385475</v>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1760,18 +1871,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,7 +1903,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1813,30 +1925,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -1858,22 +1975,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>2143</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="n">
         <v>0.9986000933271115</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.0004666355576294914</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1895,22 +2017,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="F7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
         <v>0.9717125382262997</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.0007645259938837921</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1932,22 +2059,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1138</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="n">
         <v>0.9859402460456942</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.0008787346221441124</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -1969,22 +2101,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>1134</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9929453262786596</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.002645502645502645</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2006,22 +2143,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>1026</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.5701754385964912</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.01461988304093567</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2043,22 +2185,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1006</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9910536779324056</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.001988071570576541</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2080,22 +2227,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>860</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9895348837209302</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.003488372093023256</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2117,22 +2269,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>853</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.8780773739742087</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.003516998827667058</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2154,22 +2311,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9763313609467456</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.003550295857988166</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2191,22 +2353,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13" t="n">
         <v>0.002366863905325444</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2228,22 +2395,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>810</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.9518518518518518</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.004938271604938272</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2265,22 +2437,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Acapulco</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>767</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9556714471968709</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.01303780964797914</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2302,22 +2479,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>0.9735294117647059</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.001470588235294118</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2339,22 +2521,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>664</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="13" t="n">
         <v>0.004518072289156626</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2376,22 +2563,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>0.9908814589665653</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.001519756838905775</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2413,22 +2605,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9983870967741936</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.004838709677419355</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2450,22 +2647,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9875518672199171</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2487,22 +2689,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>467</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="n">
         <v>0.9036402569593148</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.002141327623126338</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2524,22 +2731,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.002197802197802198</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2561,22 +2773,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9910714285714286</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.006696428571428571</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2598,22 +2815,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9976905311778291</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.0115473441108545</v>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -2635,22 +2857,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9907621247113164</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.006928406466512702</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2672,22 +2899,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>429</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>0.9813519813519813</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002331002331002331</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2709,22 +2941,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2746,22 +2983,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>419</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.002386634844868735</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2783,22 +3025,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>0.9878048780487805</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2820,22 +3067,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>376</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>0.9893617021276596</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.002659574468085106</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2857,22 +3109,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>0.8435754189944135</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.002793296089385475</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2894,22 +3151,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>0.9943977591036415</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.002801120448179272</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2931,22 +3193,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>334</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9910179640718563</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.005988023952095809</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -2968,22 +3235,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>331</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.945619335347432</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.006042296072507553</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3005,22 +3277,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.8792569659442725</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.009287925696594427</v>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3042,22 +3319,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="13" t="n">
         <v>0.003412969283276451</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3079,22 +3361,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13" t="n">
         <v>0.003484320557491289</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3116,22 +3403,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13" t="n">
         <v>0.8960573476702509</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.003584229390681004</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3153,22 +3445,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
         <v>0.9922178988326849</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.003891050583657588</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3190,22 +3487,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>249</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="13" t="n">
         <v>0.008032128514056224</v>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3227,22 +3529,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Mazatlán</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0.008130081300813009</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3264,22 +3571,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9915966386554622</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.01260504201680672</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3301,22 +3613,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="13" t="n">
         <v>0.9220779220779221</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.004329004329004329</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3338,22 +3655,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="13" t="n">
         <v>0.9956331877729258</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3375,22 +3697,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="n">
         <v>0.982532751091703</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3412,22 +3739,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="13" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.004484304932735426</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3449,22 +3781,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="F49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13" t="n">
         <v>0.9908675799086758</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.0045662100456621</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3486,22 +3823,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3523,22 +3865,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="13" t="n">
         <v>0.9716981132075472</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.004716981132075472</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3560,22 +3907,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="13" t="n">
         <v>0.01415094339622642</v>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3597,22 +3949,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3634,22 +3991,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="13" t="n">
+      <c r="G54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13" t="n">
         <v>0.994413407821229</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.00558659217877095</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3671,22 +4033,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9943502824858758</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.01129943502824859</v>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3703,18 +4070,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3734,7 +4102,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3756,30 +4124,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -3801,22 +4174,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>3087</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.07223841917719469</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -3838,22 +4216,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>2426</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>2363</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.9740313272877164</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3875,22 +4258,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>2163</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>2106</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.9736477115117892</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3912,22 +4300,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>1928</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>1910</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.9906639004149378</v>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3949,22 +4342,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>1588</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.1309823677581864</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -3986,22 +4384,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1301</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1289</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.9907763259031515</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4023,22 +4426,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>1209</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>636</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.5260545905707196</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -4060,22 +4468,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>1057</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>840</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.7947019867549668</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4097,22 +4510,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>995</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.995</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4134,22 +4552,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>884</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.973568281938326</v>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4171,22 +4594,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>791</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>754</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.9532237673830595</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -4208,22 +4636,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>782</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>773</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.9884910485933504</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4245,22 +4678,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>743</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>349</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.4697173620457604</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -4282,22 +4720,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>736</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>724</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.9836956521739131</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4319,22 +4762,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>727</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>727</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4356,22 +4804,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Montreal</t>
         </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>727</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>727</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4393,22 +4846,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>692</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>691</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.9985549132947977</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4430,22 +4888,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>690</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>682</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.9884057971014493</v>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4467,22 +4930,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>686</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>665</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.9693877551020408</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -4504,22 +4972,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>676</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>667</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.9866863905325444</v>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4541,22 +5014,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>662</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>625</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.9441087613293051</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -4578,22 +5056,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Montreal</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>650</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.9878419452887538</v>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4615,22 +5098,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Jacksonville Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>654</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>646</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.9877675840978594</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4652,22 +5140,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>619</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>619</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>619</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4689,22 +5182,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>603</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>602</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.9983416252072969</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4726,22 +5224,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>572</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>572</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>572</v>
+      </c>
+      <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4763,22 +5266,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>532</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.9830827067669173</v>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4800,22 +5308,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>521</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>521</v>
       </c>
       <c r="G33" s="12" t="n">
+        <v>521</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4837,22 +5350,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>514</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>508</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.9883268482490273</v>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4874,22 +5392,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>485</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.9917525773195877</v>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4911,22 +5434,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>462</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>459</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.9935064935064936</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4948,22 +5476,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>443</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>442</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.9977426636568849</v>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -4985,22 +5518,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>439</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.9840546697038725</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5022,22 +5560,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Pittsburgh Area</t>
         </is>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>433</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>433</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>433</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5059,22 +5602,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>406</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.9398148148148148</v>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5096,22 +5644,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Tampa Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>420</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>416</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.9904761904761905</v>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5133,22 +5686,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>419</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>419</v>
       </c>
       <c r="G42" s="12" t="n">
+        <v>419</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5170,22 +5728,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>416</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>414</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.9951923076923077</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5207,22 +5770,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>405</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>398</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.9827160493827161</v>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5244,22 +5812,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Sheridan Area</t>
         </is>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>400</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>400</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5281,22 +5854,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>399</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>399</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5318,22 +5896,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>399</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.9147869674185464</v>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5355,22 +5938,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>385</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.9896103896103896</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5392,22 +5980,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>382</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>374</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.9790575916230366</v>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5429,22 +6022,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>380</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.9973753280839895</v>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5466,22 +6064,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>West Palm Beach Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>379</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.9973614775725593</v>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5503,22 +6106,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>373</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.9867724867724867</v>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5540,22 +6148,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>374</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>372</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.9946524064171123</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5577,22 +6190,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>372</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>365</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.9811827956989247</v>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5614,22 +6232,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Seattle Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>370</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>366</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.9891891891891892</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5677,7 +6300,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7520,7 +8143,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9332,18 +9955,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9363,7 +9987,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9375,40 +9999,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ExternalProviderName</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -9423,27 +10052,32 @@
           <t>DerbySoft</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>210627</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>203384</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>356</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9656121959672787</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.001690191665835814</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9458,27 +10092,32 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>38582</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>35844</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>689</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9290342646830128</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.01785806852936602</v>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9493,27 +10132,32 @@
           <t>HBSI</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>16160</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>10576</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.6544554455445545</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.002846534653465346</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9528,27 +10172,32 @@
           <t>Siteminder</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>6788</v>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D9" s="12" t="n">
         <v>6788</v>
       </c>
       <c r="E9" s="12" t="n">
+        <v>6788</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="F9" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>0.03049499116087213</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9563,27 +10212,32 @@
           <t>SynXis</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>4752</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>4723</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9938973063973064</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9598,27 +10252,32 @@
           <t>Travelclick</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>1519</v>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D11" s="12" t="n">
         <v>1519</v>
       </c>
       <c r="E11" s="12" t="n">
+        <v>1519</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>0.0467412771560237</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9633,27 +10292,32 @@
           <t>Omnibees</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>316</v>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>316</v>
       </c>
       <c r="E12" s="12" t="n">
+        <v>316</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="n">
         <v>0.03164556962025317</v>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9670,18 +10334,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9701,7 +10366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9723,30 +10388,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -9768,22 +10438,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>2143</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="n">
         <v>0.9986000933271115</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.0004666355576294914</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9805,22 +10480,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1308</v>
       </c>
-      <c r="F7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
         <v>0.9717125382262997</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.0007645259938837921</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9842,22 +10522,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1138</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="n">
         <v>0.9859402460456942</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.0008787346221441124</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9879,22 +10564,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="F9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="n">
         <v>0.9735294117647059</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.001470588235294118</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9916,22 +10606,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>658</v>
       </c>
-      <c r="F10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13" t="n">
         <v>0.9908814589665653</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.001519756838905775</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9953,22 +10648,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1006</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9910536779324056</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.001988071570576541</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9990,22 +10690,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>467</v>
       </c>
-      <c r="F12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="n">
         <v>0.9036402569593148</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.002141327623126338</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10027,22 +10732,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.002197802197802198</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10064,22 +10774,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>429</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13" t="n">
         <v>0.9813519813519813</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.002331002331002331</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10101,22 +10816,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>0.6226415094339622</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.002358490566037736</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10138,22 +10858,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="13" t="n">
         <v>0.002366863905325444</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10175,22 +10900,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>419</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.002386634844868735</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10212,22 +10942,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>0.9878048780487805</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10249,22 +10984,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>1134</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9929453262786596</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.002645502645502645</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10286,22 +11026,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>376</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>0.9893617021276596</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.002659574468085106</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10323,22 +11068,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>358</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13" t="n">
         <v>0.8435754189944135</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.002793296089385475</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10360,22 +11110,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="13" t="n">
         <v>0.9943977591036415</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.002801120448179272</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10397,22 +11152,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13" t="n">
         <v>0.003412969283276451</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10434,22 +11194,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="13" t="n">
         <v>0.003484320557491289</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10471,22 +11236,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>860</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9895348837209302</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.003488372093023256</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10508,22 +11278,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>853</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.8780773739742087</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.003516998827667058</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10545,22 +11320,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>845</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9763313609467456</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.003550295857988166</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10582,22 +11362,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="n">
         <v>0.8960573476702509</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.003584229390681004</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10619,22 +11404,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="n">
         <v>0.9922178988326849</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.003891050583657588</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10656,22 +11446,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9875518672199171</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10693,22 +11488,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>0.9220779220779221</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.004329004329004329</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10730,22 +11530,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="13" t="n">
         <v>0.9956331877729258</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10767,22 +11572,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>0.982532751091703</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.004366812227074236</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10804,22 +11614,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="13" t="n">
         <v>0.004484304932735426</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10841,22 +11656,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>664</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="H35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="13" t="n">
         <v>0.004518072289156626</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10878,22 +11698,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="13" t="n">
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>0.9908675799086758</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.0045662100456621</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10915,22 +11740,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="13" t="n">
         <v>0.004651162790697674</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10952,22 +11782,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="13" t="n">
         <v>0.9716981132075472</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.004716981132075472</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10989,22 +11824,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9983870967741936</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.004838709677419355</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11026,22 +11866,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>810</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9518518518518518</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.004938271604938272</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11063,22 +11908,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
         <v>0.994413407821229</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.00558659217877095</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11100,22 +11950,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="13" t="n">
+      <c r="G42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>0.9886363636363636</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.005681818181818182</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11137,22 +11992,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Lake Tahoe Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="13" t="n">
         <v>0.9883040935672515</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.005847953216374269</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11174,22 +12034,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>334</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.9910179640718563</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.005988023952095809</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11211,22 +12076,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>331</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.945619335347432</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.006042296072507553</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11248,22 +12118,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="13" t="n">
         <v>0.006060606060606061</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11285,22 +12160,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Burlington Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="n">
         <v>0.9810126582278481</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.006329113924050633</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11322,22 +12202,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.9910714285714286</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.006696428571428571</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11359,22 +12244,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Cozumel</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="F49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13" t="n">
         <v>0.9865771812080537</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.006711409395973154</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11396,22 +12286,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="13" t="n">
         <v>0.273972602739726</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.00684931506849315</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11433,22 +12328,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>433</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9907621247113164</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.006928406466512702</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11470,22 +12370,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Bogotá Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="13" t="n">
+      <c r="G52" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="13" t="n">
         <v>0.007042253521126761</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11507,22 +12412,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>Travelclick</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="13" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>0.007042253521126761</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11544,22 +12454,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Puerto Vallarta Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="13" t="n">
+      <c r="G54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13" t="n">
         <v>0.6911764705882353</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.007352941176470588</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11581,22 +12496,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="F55" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="13" t="n">
+      <c r="G55" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="13" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.007407407407407408</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
